--- a/static/standards-correlations/North_Carolina_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/North_Carolina_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$21</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | NC Standard Course of Study, Computer Science I</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | NC Standard Course of Study, Computer Science I</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1093,7 +1094,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3F (Talking to a Server) introduces the server as a distinct role and Discovery Systems 9 covers senders, receivers, and protocols. Routers, switches, and topology are absent.</t>
+          <t>Ext 5.3F (Talking to a Server) introduces the server as a distinct role and Introductory Systems 9 covers senders, receivers, and protocols. Routers, switches, and topology are absent.</t>
         </is>
       </c>
     </row>
@@ -1342,6 +1343,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1386,7 +1388,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1400,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -1498,6 +1500,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
@@ -1520,7 +1524,7 @@
 SOURCE NOTE: Codes and statements transcribed from the CodeHS published North Carolina Computer Science I framework; internal CodeHS unit references (U3-L1 style) appearing in the source have been stripped. The graduation requirement, statute, and 80 percent alignment test were verified against NCDPI. Verify wording against the official NCSCOS document before any formal submission.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
